--- a/Result/profitability/3523.xlsx
+++ b/Result/profitability/3523.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.54</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.33125</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-65.96374999999999</v>
+        <v>-64.96499999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.58</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0575</v>
+        <v>-0.02625000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>-57.82499999999999</v>
+        <v>-46.96249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07875</v>
+        <v>0.07749999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-41.16749999999999</v>
+        <v>-41.56749999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.007500000000000007</v>
+        <v>0.02625</v>
       </c>
       <c r="N5" t="n">
-        <v>-35.28374999999999</v>
+        <v>-28.48624999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05749999999999999</v>
+        <v>0.06124999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.68999999999999</v>
+        <v>-25.13499999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01624999999999999</v>
+        <v>-0.04500000000000003</v>
       </c>
       <c r="N7" t="n">
-        <v>-20.95624999999999</v>
+        <v>-1.567499999999989</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.48</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06999999999999998</v>
+        <v>0.07124999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>5.310000000000011</v>
+        <v>12.65250000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3523</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>28</v>
+      </c>
+      <c r="D75" t="n">
+        <v>36</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-29.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-27</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-96.72%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-27</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-28</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.45375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-73.38499999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.02222222222222225</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>58.73999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.6631293745766539</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2542372881355932</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.6456898598907623</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
